--- a/Outputs/Scenarios/PtX_demand_LV_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LV_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001613032710587493</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002259962741233266</v>
+        <v>0.002448378737498125</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0005084830399946095</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.004519925482466532</v>
+        <v>0.004067864319956876</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>2.324107095311647e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0007533209137444221</v>
+        <v>0.0005084830399946095</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002387898547100426</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0121983626792029</v>
+        <v>0.0132153558424388</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.002744585308823753</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0243967253584058</v>
+        <v>0.02195668247059003</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001256788709000225</v>
       </c>
       <c r="K42" t="n">
-        <v>0.004066120893067634</v>
+        <v>0.002744585308823753</v>
       </c>
     </row>
     <row r="43">
